--- a/upload/limites_lrf.xlsx
+++ b/upload/limites_lrf.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB262E38-DFD7-4F06-B814-506BE6789219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="19755" yWindow="0" windowWidth="18645" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="limites_lrf" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
   <si>
     <t xml:space="preserve"> -   </t>
   </si>
@@ -73,13 +74,16 @@
   </si>
   <si>
     <t>limite_alerta</t>
+  </si>
+  <si>
+    <t>jan_2023_a_dez_2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -590,10 +594,10 @@
     <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Incorreto" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Neutra" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Ruim" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Saída" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Texto de Aviso" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Texto Explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
@@ -933,25 +937,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="89.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="90.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="121.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="100.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="60.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="54.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="59.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="60.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="59.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="59" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="9.125" style="1"/>
+    <col min="12" max="13" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -986,7 +990,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1021,7 +1025,7 @@
         <v>49269730443.543549</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1056,7 +1060,7 @@
         <v>48204299921</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1091,7 +1095,7 @@
         <v>47036013560.989998</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1126,7 +1130,7 @@
         <v>45628385385.599998</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1161,7 +1165,7 @@
         <v>43710718165.160004</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1194,6 +1198,41 @@
       </c>
       <c r="K7" s="1">
         <v>42232845652.330002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1">
+        <v>92079439352.229996</v>
+      </c>
+      <c r="C8" s="1">
+        <v>82167184.640000001</v>
+      </c>
+      <c r="D8" s="1">
+        <v>18522957</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>91978749210.589996</v>
+      </c>
+      <c r="H8" s="1">
+        <v>47245316457.129997</v>
+      </c>
+      <c r="I8" s="1">
+        <v>45069587113.190002</v>
+      </c>
+      <c r="J8" s="1">
+        <v>42816107757.529999</v>
+      </c>
+      <c r="K8" s="1">
+        <v>40562628401.870003</v>
       </c>
     </row>
   </sheetData>

--- a/upload/limites_lrf.xlsx
+++ b/upload/limites_lrf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB262E38-DFD7-4F06-B814-506BE6789219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F852AA-6FD8-4C6F-A43D-7C741F3CBB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19755" yWindow="0" windowWidth="18645" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
   <si>
     <t xml:space="preserve"> -   </t>
   </si>
@@ -76,7 +76,22 @@
     <t>limite_alerta</t>
   </si>
   <si>
-    <t>jan_2023_a_dez_2024</t>
+    <t>jan_2023_a_dez_2023</t>
+  </si>
+  <si>
+    <t>jan_2022_a_dez_2022</t>
+  </si>
+  <si>
+    <t>mai_2021_a_abr_2022</t>
+  </si>
+  <si>
+    <t>set_2021_a_ago_2022</t>
+  </si>
+  <si>
+    <t>set_2022_a_ago_2023</t>
+  </si>
+  <si>
+    <t>mai_2022_a_abr_2023</t>
   </si>
 </sst>
 </file>
@@ -938,7 +953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -1235,6 +1250,181 @@
         <v>40562628401.870003</v>
       </c>
     </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1">
+        <v>91042853012.449997</v>
+      </c>
+      <c r="C9" s="1">
+        <v>48189557.640000001</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>90994663454.809998</v>
+      </c>
+      <c r="H9" s="1">
+        <v>45152056960.169998</v>
+      </c>
+      <c r="I9" s="1">
+        <v>44587385092.860001</v>
+      </c>
+      <c r="J9" s="1">
+        <v>42358015838.209999</v>
+      </c>
+      <c r="K9" s="1">
+        <v>40128646583.57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1">
+        <v>91603261503.279999</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4513900</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>91598747603.279999</v>
+      </c>
+      <c r="H10" s="1">
+        <v>45177551751.260002</v>
+      </c>
+      <c r="I10" s="1">
+        <v>44883386325.610001</v>
+      </c>
+      <c r="J10" s="1">
+        <v>42639217009.330002</v>
+      </c>
+      <c r="K10" s="1">
+        <v>40395047693.050003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1">
+        <v>91405979912.770004</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2103000</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>91403876912.770004</v>
+      </c>
+      <c r="H11" s="1">
+        <v>44272473951.82</v>
+      </c>
+      <c r="I11" s="1">
+        <v>44787899687.260002</v>
+      </c>
+      <c r="J11" s="1">
+        <v>42548504702.889999</v>
+      </c>
+      <c r="K11" s="1">
+        <v>40309109718.529999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1">
+        <v>89048963672.639999</v>
+      </c>
+      <c r="C12" s="1">
+        <v>20325208</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>89028638464.639999</v>
+      </c>
+      <c r="H12" s="1">
+        <v>43503340635.309998</v>
+      </c>
+      <c r="I12" s="1">
+        <v>43624032847.669998</v>
+      </c>
+      <c r="J12" s="1">
+        <v>41442831205.290001</v>
+      </c>
+      <c r="K12" s="1">
+        <v>39261629562.910004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1">
+        <v>86411512663.570007</v>
+      </c>
+      <c r="C13" s="1">
+        <v>21025208</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>86390487455.570007</v>
+      </c>
+      <c r="H13" s="1">
+        <v>41431933768.550003</v>
+      </c>
+      <c r="I13" s="1">
+        <v>42331338853.230003</v>
+      </c>
+      <c r="J13" s="1">
+        <v>40214771910.57</v>
+      </c>
+      <c r="K13" s="1">
+        <v>38098204967.910004</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
